--- a/cal.xlsx
+++ b/cal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Workspace\dev\projects\nexusapi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBF1A892-FF59-4B38-836F-DF9BB1A8476D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8DDAB704-9197-4C72-8104-C38EFE420B8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{16243A16-D9D0-4BAA-BB81-C043C32BFA90}"/>
   </bookViews>
@@ -17,6 +17,7 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="40">
   <si>
     <t>Tên Gói</t>
   </si>
@@ -131,6 +132,24 @@
   </si>
   <si>
     <t>Gban Cache (đ/1)</t>
+  </si>
+  <si>
+    <t>gpt-5.4-nano</t>
+  </si>
+  <si>
+    <t>gpt-5.4</t>
+  </si>
+  <si>
+    <t>GPT-5.3-Codex</t>
+  </si>
+  <si>
+    <t>o3-deep-research</t>
+  </si>
+  <si>
+    <t>text-embedding-3-large</t>
+  </si>
+  <si>
+    <t>text-embedding-3-small</t>
   </si>
 </sst>
 </file>
@@ -139,8 +158,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="169" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="174" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -251,7 +270,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -277,13 +296,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="174" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -292,6 +311,10 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -689,18 +712,18 @@
         <v>200000</v>
       </c>
       <c r="C5" s="11">
-        <f t="shared" ref="C5:C7" si="0">B5/$B$2</f>
+        <f>B5/$B$2</f>
         <v>8000</v>
       </c>
       <c r="D5" s="12">
         <v>0.05</v>
       </c>
       <c r="E5" s="11">
-        <f t="shared" ref="E5:E7" si="1">C5+D5*C5</f>
+        <f>C5+D5*C5</f>
         <v>8400</v>
       </c>
       <c r="F5" s="13">
-        <f t="shared" ref="F5:F7" si="2">B5/E5</f>
+        <f>B5/E5</f>
         <v>23.80952380952381</v>
       </c>
     </row>
@@ -712,18 +735,18 @@
         <v>500000</v>
       </c>
       <c r="C6" s="11">
-        <f t="shared" si="0"/>
+        <f>B6/$B$2</f>
         <v>20000</v>
       </c>
       <c r="D6" s="12">
         <v>0.1</v>
       </c>
       <c r="E6" s="11">
-        <f t="shared" si="1"/>
+        <f>C6+D6*C6</f>
         <v>22000</v>
       </c>
       <c r="F6" s="13">
-        <f t="shared" si="2"/>
+        <f>B6/E6</f>
         <v>22.727272727272727</v>
       </c>
     </row>
@@ -735,18 +758,18 @@
         <v>2000000</v>
       </c>
       <c r="C7" s="11">
-        <f t="shared" si="0"/>
+        <f>B7/$B$2</f>
         <v>80000</v>
       </c>
       <c r="D7" s="12">
         <v>0.15</v>
       </c>
       <c r="E7" s="11">
-        <f t="shared" si="1"/>
+        <f>C7+D7*C7</f>
         <v>92000</v>
       </c>
       <c r="F7" s="13">
-        <f t="shared" si="2"/>
+        <f>B7/E7</f>
         <v>21.739130434782609</v>
       </c>
     </row>
@@ -758,10 +781,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CC63B8F-9FCA-4298-8A55-052794063237}">
-  <dimension ref="A1:R20"/>
+  <dimension ref="A1:R21"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.44140625" bestFit="1" customWidth="1"/>
@@ -776,7 +799,7 @@
     <col min="13" max="13" width="14.88671875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="16.33203125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.109375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="9.77734375" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="13.21875" bestFit="1" customWidth="1"/>
   </cols>
@@ -892,7 +915,7 @@
         <f>L2/Sheet1!$B$2</f>
         <v>9.7199999999999999E-4</v>
       </c>
-      <c r="P2" s="3">
+      <c r="P2" s="16">
         <v>128000</v>
       </c>
       <c r="Q2" s="3">
@@ -921,7 +944,7 @@
         <v>4.5</v>
       </c>
       <c r="F3" s="3">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="G3" s="3">
         <f>C3*Sheet1!$B$1/1000000</f>
@@ -937,267 +960,330 @@
       </c>
       <c r="J3" s="3">
         <f>G3*F3</f>
-        <v>2.6325000000000001E-2</v>
+        <v>3.0374999999999999E-2</v>
       </c>
       <c r="K3" s="3">
         <f t="shared" ref="K3:K20" si="0">H3*F3</f>
-        <v>2.8080000000000002E-3</v>
+        <v>3.2399999999999998E-3</v>
       </c>
       <c r="L3" s="3">
         <f t="shared" ref="L3:L20" si="1">I3*F3</f>
-        <v>0.15795000000000001</v>
+        <v>0.18225</v>
       </c>
       <c r="M3" s="3">
         <f>J3/Sheet1!$B$2</f>
-        <v>1.0530000000000001E-3</v>
+        <v>1.2149999999999999E-3</v>
       </c>
       <c r="N3" s="3">
         <f>K3/Sheet1!$B$2</f>
-        <v>1.1232000000000001E-4</v>
+        <v>1.2960000000000001E-4</v>
       </c>
       <c r="O3" s="3">
         <f>L3/Sheet1!$B$2</f>
-        <v>6.3180000000000007E-3</v>
-      </c>
-      <c r="P3" s="3">
+        <v>7.2899999999999996E-3</v>
+      </c>
+      <c r="P3" s="16">
         <v>400000</v>
       </c>
       <c r="Q3" s="3">
         <f t="shared" ref="Q3:Q20" si="2">ROUND(P3*M3*0.5,0)</f>
-        <v>211</v>
+        <v>243</v>
       </c>
       <c r="R3" s="4">
         <f t="shared" ref="R3:R20" si="3">(J3-G3)/J3</f>
-        <v>0.23076923076923078</v>
+        <v>0.33333333333333331</v>
       </c>
     </row>
     <row r="4" spans="1:18">
+      <c r="A4" t="s">
+        <v>34</v>
+      </c>
       <c r="B4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
+      <c r="C4" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="D4" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="E4" s="3">
+        <v>1.25</v>
+      </c>
+      <c r="F4" s="3">
+        <v>1</v>
+      </c>
       <c r="G4" s="3">
         <f>C4*Sheet1!$B$1/1000000</f>
-        <v>0</v>
+        <v>5.4000000000000003E-3</v>
       </c>
       <c r="H4" s="3">
         <f>D4*Sheet1!$B$1/1000000</f>
-        <v>0</v>
+        <v>5.4000000000000001E-4</v>
       </c>
       <c r="I4" s="3">
         <f>E4*Sheet1!$B$1/1000000</f>
-        <v>0</v>
+        <v>3.3750000000000002E-2</v>
       </c>
       <c r="J4" s="3">
-        <f t="shared" ref="J3:J20" si="4">G4*F4</f>
-        <v>0</v>
+        <f t="shared" ref="J4:J20" si="4">G4*F4</f>
+        <v>5.4000000000000003E-3</v>
       </c>
       <c r="K4" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5.4000000000000001E-4</v>
       </c>
       <c r="L4" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3.3750000000000002E-2</v>
       </c>
       <c r="M4" s="3">
         <f>J4/Sheet1!$B$2</f>
-        <v>0</v>
+        <v>2.1600000000000002E-4</v>
       </c>
       <c r="N4" s="3">
         <f>K4/Sheet1!$B$2</f>
-        <v>0</v>
+        <v>2.16E-5</v>
       </c>
       <c r="O4" s="3">
         <f>L4/Sheet1!$B$2</f>
-        <v>0</v>
-      </c>
-      <c r="P4" s="3"/>
+        <v>1.3500000000000001E-3</v>
+      </c>
+      <c r="P4" s="16">
+        <v>400000</v>
+      </c>
       <c r="Q4" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R4" s="4" t="e">
+        <v>43</v>
+      </c>
+      <c r="R4" s="4">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:18">
+      <c r="A5" t="s">
+        <v>35</v>
+      </c>
       <c r="B5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
+      <c r="C5" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="E5" s="3">
+        <v>15</v>
+      </c>
+      <c r="F5" s="3">
+        <v>1.2</v>
+      </c>
       <c r="G5" s="3">
         <f>C5*Sheet1!$B$1/1000000</f>
-        <v>0</v>
+        <v>6.7500000000000004E-2</v>
       </c>
       <c r="H5" s="3">
         <f>D5*Sheet1!$B$1/1000000</f>
-        <v>0</v>
+        <v>6.7499999999999999E-3</v>
       </c>
       <c r="I5" s="3">
         <f>E5*Sheet1!$B$1/1000000</f>
-        <v>0</v>
+        <v>0.40500000000000003</v>
       </c>
       <c r="J5" s="3">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8.1000000000000003E-2</v>
       </c>
       <c r="K5" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8.0999999999999996E-3</v>
       </c>
       <c r="L5" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.48599999999999999</v>
       </c>
       <c r="M5" s="3">
         <f>J5/Sheet1!$B$2</f>
-        <v>0</v>
+        <v>3.2400000000000003E-3</v>
       </c>
       <c r="N5" s="3">
         <f>K5/Sheet1!$B$2</f>
-        <v>0</v>
+        <v>3.2399999999999996E-4</v>
       </c>
       <c r="O5" s="3">
         <f>L5/Sheet1!$B$2</f>
-        <v>0</v>
-      </c>
-      <c r="P5" s="3"/>
+        <v>1.9439999999999999E-2</v>
+      </c>
+      <c r="P5" s="16">
+        <v>1050000</v>
+      </c>
       <c r="Q5" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R5" s="4" t="e">
+        <v>1701</v>
+      </c>
+      <c r="R5" s="4">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
+        <v>0.16666666666666663</v>
       </c>
     </row>
     <row r="6" spans="1:18">
+      <c r="A6" t="s">
+        <v>36</v>
+      </c>
       <c r="B6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
+      <c r="C6" s="3">
+        <v>1.75</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0.18</v>
+      </c>
+      <c r="E6" s="3">
+        <v>14</v>
+      </c>
+      <c r="F6" s="3">
+        <v>1.2</v>
+      </c>
       <c r="G6" s="3">
         <f>C6*Sheet1!$B$1/1000000</f>
-        <v>0</v>
+        <v>4.725E-2</v>
       </c>
       <c r="H6" s="3">
         <f>D6*Sheet1!$B$1/1000000</f>
-        <v>0</v>
+        <v>4.8599999999999997E-3</v>
       </c>
       <c r="I6" s="3">
         <f>E6*Sheet1!$B$1/1000000</f>
-        <v>0</v>
+        <v>0.378</v>
       </c>
       <c r="J6" s="3">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5.67E-2</v>
       </c>
       <c r="K6" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5.8319999999999995E-3</v>
       </c>
       <c r="L6" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.4536</v>
       </c>
       <c r="M6" s="3">
         <f>J6/Sheet1!$B$2</f>
-        <v>0</v>
+        <v>2.2680000000000001E-3</v>
       </c>
       <c r="N6" s="3">
         <f>K6/Sheet1!$B$2</f>
-        <v>0</v>
+        <v>2.3327999999999999E-4</v>
       </c>
       <c r="O6" s="3">
         <f>L6/Sheet1!$B$2</f>
-        <v>0</v>
-      </c>
-      <c r="P6" s="3"/>
+        <v>1.8144E-2</v>
+      </c>
+      <c r="P6" s="16">
+        <v>400000</v>
+      </c>
       <c r="Q6" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R6" s="4" t="e">
+        <v>454</v>
+      </c>
+      <c r="R6" s="4">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
+        <v>0.16666666666666666</v>
       </c>
     </row>
     <row r="7" spans="1:18">
+      <c r="A7" t="s">
+        <v>37</v>
+      </c>
       <c r="B7" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
+      <c r="C7" s="3">
+        <v>10</v>
+      </c>
+      <c r="D7" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="E7" s="3">
+        <v>40</v>
+      </c>
+      <c r="F7" s="3">
+        <v>1.1000000000000001</v>
+      </c>
       <c r="G7" s="3">
         <f>C7*Sheet1!$B$1/1000000</f>
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="H7" s="3">
         <f>D7*Sheet1!$B$1/1000000</f>
-        <v>0</v>
+        <v>6.7500000000000004E-2</v>
       </c>
       <c r="I7" s="3">
         <f>E7*Sheet1!$B$1/1000000</f>
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="J7" s="3">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.29700000000000004</v>
       </c>
       <c r="K7" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>7.425000000000001E-2</v>
       </c>
       <c r="L7" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.1880000000000002</v>
       </c>
       <c r="M7" s="3">
         <f>J7/Sheet1!$B$2</f>
-        <v>0</v>
+        <v>1.1880000000000002E-2</v>
       </c>
       <c r="N7" s="3">
         <f>K7/Sheet1!$B$2</f>
-        <v>0</v>
+        <v>2.9700000000000004E-3</v>
       </c>
       <c r="O7" s="3">
         <f>L7/Sheet1!$B$2</f>
-        <v>0</v>
-      </c>
-      <c r="P7" s="3"/>
+        <v>4.7520000000000007E-2</v>
+      </c>
+      <c r="P7" s="16">
+        <v>200000</v>
+      </c>
       <c r="Q7" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R7" s="4" t="e">
+        <v>1188</v>
+      </c>
+      <c r="R7" s="4">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
+        <v>9.0909090909090981E-2</v>
       </c>
     </row>
     <row r="8" spans="1:18">
+      <c r="A8" t="s">
+        <v>38</v>
+      </c>
       <c r="B8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
+      <c r="C8" s="3">
+        <v>0.13</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>1.8</v>
+      </c>
       <c r="G8" s="3">
         <f>C8*Sheet1!$B$1/1000000</f>
-        <v>0</v>
+        <v>3.5100000000000001E-3</v>
       </c>
       <c r="H8" s="3">
         <f>D8*Sheet1!$B$1/1000000</f>
@@ -1209,7 +1295,7 @@
       </c>
       <c r="J8" s="3">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6.3180000000000007E-3</v>
       </c>
       <c r="K8" s="3">
         <f t="shared" si="0"/>
@@ -1221,7 +1307,7 @@
       </c>
       <c r="M8" s="3">
         <f>J8/Sheet1!$B$2</f>
-        <v>0</v>
+        <v>2.5272000000000001E-4</v>
       </c>
       <c r="N8" s="3">
         <f>K8/Sheet1!$B$2</f>
@@ -1231,27 +1317,36 @@
         <f>L8/Sheet1!$B$2</f>
         <v>0</v>
       </c>
-      <c r="P8" s="3"/>
+      <c r="P8" s="16">
+        <v>200000</v>
+      </c>
       <c r="Q8" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R8" s="4" t="e">
+        <v>25</v>
+      </c>
+      <c r="R8" s="4">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
+        <v>0.44444444444444448</v>
       </c>
     </row>
     <row r="9" spans="1:18">
+      <c r="A9" t="s">
+        <v>39</v>
+      </c>
       <c r="B9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="3"/>
+      <c r="C9" s="3">
+        <v>0.02</v>
+      </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
+      <c r="F9" s="3">
+        <v>2</v>
+      </c>
       <c r="G9" s="3">
         <f>C9*Sheet1!$B$1/1000000</f>
-        <v>0</v>
+        <v>5.4000000000000001E-4</v>
       </c>
       <c r="H9" s="3">
         <f>D9*Sheet1!$B$1/1000000</f>
@@ -1263,7 +1358,7 @@
       </c>
       <c r="J9" s="3">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.08E-3</v>
       </c>
       <c r="K9" s="3">
         <f t="shared" si="0"/>
@@ -1275,7 +1370,7 @@
       </c>
       <c r="M9" s="3">
         <f>J9/Sheet1!$B$2</f>
-        <v>0</v>
+        <v>4.32E-5</v>
       </c>
       <c r="N9" s="3">
         <f>K9/Sheet1!$B$2</f>
@@ -1285,14 +1380,16 @@
         <f>L9/Sheet1!$B$2</f>
         <v>0</v>
       </c>
-      <c r="P9" s="3"/>
+      <c r="P9" s="16">
+        <v>200000</v>
+      </c>
       <c r="Q9" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R9" s="4" t="e">
+        <v>4</v>
+      </c>
+      <c r="R9" s="4">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1339,7 +1436,7 @@
         <f>L10/Sheet1!$B$2</f>
         <v>0</v>
       </c>
-      <c r="P10" s="3"/>
+      <c r="P10" s="16"/>
       <c r="Q10" s="3">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -1393,7 +1490,7 @@
         <f>L11/Sheet1!$B$2</f>
         <v>0</v>
       </c>
-      <c r="P11" s="3"/>
+      <c r="P11" s="16"/>
       <c r="Q11" s="3">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -1447,7 +1544,7 @@
         <f>L12/Sheet1!$B$2</f>
         <v>0</v>
       </c>
-      <c r="P12" s="3"/>
+      <c r="P12" s="16"/>
       <c r="Q12" s="3">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -1501,7 +1598,7 @@
         <f>L13/Sheet1!$B$2</f>
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
+      <c r="P13" s="16"/>
       <c r="Q13" s="3">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -1555,7 +1652,7 @@
         <f>L14/Sheet1!$B$2</f>
         <v>0</v>
       </c>
-      <c r="P14" s="3"/>
+      <c r="P14" s="16"/>
       <c r="Q14" s="3">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -1609,7 +1706,7 @@
         <f>L15/Sheet1!$B$2</f>
         <v>0</v>
       </c>
-      <c r="P15" s="3"/>
+      <c r="P15" s="16"/>
       <c r="Q15" s="3">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -1663,7 +1760,7 @@
         <f>L16/Sheet1!$B$2</f>
         <v>0</v>
       </c>
-      <c r="P16" s="3"/>
+      <c r="P16" s="16"/>
       <c r="Q16" s="3">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -1717,7 +1814,7 @@
         <f>L17/Sheet1!$B$2</f>
         <v>0</v>
       </c>
-      <c r="P17" s="3"/>
+      <c r="P17" s="16"/>
       <c r="Q17" s="3">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -1771,7 +1868,7 @@
         <f>L18/Sheet1!$B$2</f>
         <v>0</v>
       </c>
-      <c r="P18" s="3"/>
+      <c r="P18" s="16"/>
       <c r="Q18" s="3">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -1825,7 +1922,7 @@
         <f>L19/Sheet1!$B$2</f>
         <v>0</v>
       </c>
-      <c r="P19" s="3"/>
+      <c r="P19" s="16"/>
       <c r="Q19" s="3">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -1879,7 +1976,7 @@
         <f>L20/Sheet1!$B$2</f>
         <v>0</v>
       </c>
-      <c r="P20" s="3"/>
+      <c r="P20" s="16"/>
       <c r="Q20" s="3">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -1889,7 +1986,11 @@
         <v>#DIV/0!</v>
       </c>
     </row>
+    <row r="21" spans="2:18">
+      <c r="P21" s="17"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>